--- a/data/Morphology_for_mortality_LOOKUP.xlsx
+++ b/data/Morphology_for_mortality_LOOKUP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp.sharepoint.com/sites/usgs-carbonate_budget_restoration_tool/Shared Documents/Carbonate Budget Tool Collaboration/Carbonate_Budget_Tool_Code/CarbonateBudgetRestorationTool/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{1E88727E-2A26-494B-B39C-3F384BE560B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10324C06-AEE9-4E20-B8E6-96421EA65771}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965C8B89-B65A-49DB-A120-F35604963FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" xr2:uid="{C7DFE6D2-352A-4F16-9E1F-E0C145796F9C}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11339" xr2:uid="{C7DFE6D2-352A-4F16-9E1F-E0C145796F9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -328,7 +328,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1528,7 +1527,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
@@ -1559,17 +1558,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca57789ecb406bb7a99068f68ac4c0ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89dc4794f4784a0bac47690674a3da53" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -1764,6 +1752,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1774,17 +1773,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FDF4131-9904-4A7E-AF05-997091E250F3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8AD7744-239F-4470-A05F-CDA93074D8D6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1803,6 +1791,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FDF4131-9904-4A7E-AF05-997091E250F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35848900-04C5-49C3-B817-BC09507D7535}">
   <ds:schemaRefs>
